--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484237_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484237_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1658</v>
+        <v>5.4091</v>
       </c>
       <c r="E2" t="n">
-        <v>2.841</v>
+        <v>3.0026</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3248</v>
+        <v>2.4065</v>
       </c>
       <c r="G2" t="n">
         <v>6.114</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8964</v>
+        <v>1.1397</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0083</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="n">
-        <v>0.888</v>
+        <v>0.9697</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0633</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3693</v>
+        <v>3.6205</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0716</v>
+        <v>2.1321</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2977</v>
+        <v>1.4884</v>
       </c>
       <c r="G3" t="n">
         <v>3.5103</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7269</v>
+        <v>0.9781</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1294</v>
+        <v>0.1899</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5975</v>
+        <v>0.7882</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0633</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9164</v>
+        <v>1.7287</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2521</v>
+        <v>0.4363</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6642</v>
+        <v>1.2924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3358</v>
+        <v>-2.1802</v>
       </c>
       <c r="H4" t="n">
-        <v>1.429</v>
+        <v>0.8005</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0932</v>
+        <v>-2.9806</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4951</v>
+        <v>-0.4069</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3737</v>
+        <v>1.494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1214</v>
+        <v>-1.9009</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1593</v>
+        <v>-1.7733</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0553</v>
+        <v>-0.6935</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2146</v>
+        <v>-1.0797</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7173</v>
+        <v>0.1898</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7886</v>
+        <v>-0.3754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9287</v>
+        <v>0.5653</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3321</v>
+        <v>2.547</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0549</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3939</v>
+        <v>1.3918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6385</v>
+        <v>0.8365</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7554</v>
+        <v>0.5553</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1802</v>
+        <v>0.3358</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8005</v>
+        <v>1.429</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9806</v>
+        <v>-1.0932</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4069</v>
+        <v>1.4951</v>
       </c>
       <c r="K5" t="n">
-        <v>1.494</v>
+        <v>1.3737</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9009</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7733</v>
+        <v>-1.1593</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6935</v>
+        <v>0.0553</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0797</v>
+        <v>-1.2146</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.855</v>
+        <v>1.1927</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1732</v>
+        <v>0.3729</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0283</v>
+        <v>0.8198</v>
       </c>
       <c r="V5" t="n">
-        <v>2.547</v>
+        <v>-0.3321</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3283</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3307</v>
+        <v>0.8696</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3728</v>
+        <v>0.1933</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7036</v>
+        <v>0.6763</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7343</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2102</v>
+        <v>0.749</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6052</v>
+        <v>-0.0391</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8154</v>
+        <v>0.7882</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0529</v>
+        <v>0.5373</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7447</v>
+        <v>-2.1786</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7976</v>
+        <v>2.7159</v>
       </c>
       <c r="G7" t="n">
         <v>0.036</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4159</v>
+        <v>0.9003</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6657</v>
+        <v>-0.0997</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0817</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3991</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2792</v>
+        <v>-0.4093</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.038</v>
+        <v>-0.9774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7588</v>
+        <v>0.5681</v>
       </c>
       <c r="G8" t="n">
         <v>1.1709</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3433</v>
+        <v>0.2132</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>-0.2421</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6459</v>
+        <v>0.4553</v>
       </c>
       <c r="V8" t="n">
         <v>0.9414</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.6318</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5085</v>
+        <v>-0.8793</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9436</v>
+        <v>0.2475</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6578000000000001</v>
+        <v>1.0912</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3479</v>
+        <v>0.4971</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3099</v>
+        <v>0.5942</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7376</v>
+        <v>2.5949</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>1.6739</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-1.5036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3492</v>
+        <v>-0.4239</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2694</v>
+        <v>-1.0797</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0944</v>
+        <v>-0.1603</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3715</v>
+        <v>-0.544</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7229</v>
+        <v>0.3837</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1258</v>
+        <v>-1.1951</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1826</v>
+        <v>-1.8119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0568</v>
+        <v>0.6168</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0912</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4971</v>
+        <v>0.3479</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5942</v>
+        <v>0.3099</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5949</v>
+        <v>0.7376</v>
       </c>
       <c r="K10" t="n">
-        <v>0.921</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6739</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5036</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4239</v>
+        <v>-0.3492</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0797</v>
+        <v>0.2694</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6543</v>
+        <v>0.4643</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.193</v>
+        <v>0.3961</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.3405</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6763</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1162</v>
+        <v>-1.4316</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4101</v>
+        <v>0.7134</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5263</v>
+        <v>-2.145</v>
       </c>
       <c r="G11" t="n">
         <v>0.4831</v>
@@ -1312,13 +1312,13 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0719</v>
+        <v>-0.3872</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2851</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9414</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1669</v>
+        <v>-1.6106</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1202</v>
+        <v>-0.918</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0467</v>
+        <v>-0.6926</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9048</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.09</v>
+        <v>-0.5337</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3032</v>
+        <v>0.0508</v>
       </c>
       <c r="V12" t="n">
         <v>0.6093</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.975900000000001</v>
+        <v>8.278599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2465000000000006</v>
+        <v>0.5490000000000009</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7295</v>
+        <v>7.729599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>9.579800000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.7207</v>
       </c>
       <c r="S13" t="n">
-        <v>4.443199999999999</v>
+        <v>4.745900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8698</v>
+        <v>-1.5675</v>
       </c>
       <c r="U13" t="n">
-        <v>6.313099999999999</v>
+        <v>6.313299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1639</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6856</v>
+        <v>5.2534</v>
       </c>
       <c r="E14" t="n">
-        <v>4.26</v>
+        <v>4.6644</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4256</v>
+        <v>0.589</v>
       </c>
       <c r="G14" t="n">
         <v>3.764</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.352</v>
+        <v>-0.7841</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4525</v>
+        <v>-1.0481</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1006</v>
+        <v>0.264</v>
       </c>
       <c r="V14" t="n">
         <v>1.8828</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2532</v>
+        <v>4.3271</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3173</v>
+        <v>3.4184</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9359</v>
+        <v>0.9087</v>
       </c>
       <c r="G15" t="n">
         <v>0.9103</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9343</v>
+        <v>-0.8605</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.8067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0265</v>
+        <v>-0.0537</v>
       </c>
       <c r="V15" t="n">
         <v>2.7145</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3042</v>
+        <v>1.6505</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5505</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7537</v>
+        <v>0.9988</v>
       </c>
       <c r="G16" t="n">
         <v>1.9412</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1764</v>
+        <v>-0.8302</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6252</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9405</v>
+        <v>0.1704</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4114</v>
+        <v>-2.0181</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3519</v>
+        <v>2.1885</v>
       </c>
       <c r="G17" t="n">
         <v>0.9889</v>
@@ -1780,13 +1780,13 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.733</v>
+        <v>-0.0371</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4404</v>
+        <v>-0.1663</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2926</v>
+        <v>0.1292</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3011</v>
+        <v>-0.309</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3868</v>
+        <v>-0.2856</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0856</v>
+        <v>-0.0233</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6462</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.268</v>
+        <v>-0.2758</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3978</v>
+        <v>0.2888</v>
       </c>
       <c r="V18" t="n">
         <v>0.8317</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4944</v>
+        <v>-1.2455</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.631</v>
+        <v>-0.3277</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.9179</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2124</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2317</v>
+        <v>0.0172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4341</v>
+        <v>0.3796</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2224</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9031</v>
+        <v>-1.802</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3634</v>
+        <v>-1.2622</v>
       </c>
       <c r="F20" t="n">
         <v>-0.5397</v>
@@ -2014,10 +2014,10 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6466</v>
+        <v>-0.5454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="U20" t="n">
         <v>0.2008</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2735</v>
+        <v>-2.3062</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5313</v>
+        <v>-2.2675</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7422</v>
+        <v>-0.0387</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.37</v>
+        <v>-4.5085</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6122</v>
+        <v>-1.8383</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2422</v>
+        <v>-2.6701</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.448</v>
+        <v>-2.3913</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0167</v>
+        <v>0.1433</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4313</v>
+        <v>-2.5345</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9221</v>
+        <v>-2.1172</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5956</v>
+        <v>-1.9816</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6735</v>
+        <v>-0.1356</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0026</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4404</v>
+        <v>-0.3954</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5622</v>
+        <v>0.3205</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8828</v>
+        <v>1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.3283</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3412</v>
+        <v>-2.8791</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1664</v>
+        <v>-2.1521</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1748</v>
+        <v>-0.7269</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5085</v>
+        <v>-0.0584</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8383</v>
+        <v>-2.5943</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6701</v>
+        <v>2.5359</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3913</v>
+        <v>1.659</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1433</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.5345</v>
+        <v>2.5365</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1172</v>
+        <v>-1.7174</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9816</v>
+        <v>-1.7168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1356</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.11</v>
+        <v>-0.6486</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2943</v>
+        <v>-0.6857</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1843</v>
+        <v>0.037</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4959</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0074</v>
+        <v>-3.0436</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2533</v>
+        <v>-2.138</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7542</v>
+        <v>-0.9056</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0584</v>
+        <v>-2.37</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5943</v>
+        <v>-2.6122</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5359</v>
+        <v>0.2422</v>
       </c>
       <c r="J23" t="n">
-        <v>1.659</v>
+        <v>-0.448</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="L23" t="n">
-        <v>2.5365</v>
+        <v>-0.4313</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7174</v>
+        <v>-1.9221</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7168</v>
+        <v>-2.5956</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6735</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.777</v>
+        <v>0.2325</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1663</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0098</v>
+        <v>0.3988</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>-1.8828</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6111</v>
+        <v>-3.6928</v>
       </c>
       <c r="E24" t="n">
         <v>-3.5473</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0638</v>
+        <v>-0.1455</v>
       </c>
       <c r="G24" t="n">
         <v>-3.287</v>
@@ -2326,13 +2326,13 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1288</v>
+        <v>-0.2105</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1133</v>
+        <v>0.0316</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2276</v>
+        <v>-4.0993</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5666</v>
+        <v>-2.4655</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.661</v>
+        <v>-1.6338</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6502</v>
@@ -2404,13 +2404,13 @@
         <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5541</v>
+        <v>-0.4257</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6052</v>
+        <v>-0.5041</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0511</v>
+        <v>0.0784</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2186</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.975899999999999</v>
+        <v>-7.976100000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.729700000000001</v>
+        <v>-7.729500000000002</v>
       </c>
       <c r="F26" t="n">
         <v>-0.2463999999999995</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.5802</v>
+        <v>-9.580199999999998</v>
       </c>
       <c r="H26" t="n">
         <v>-17.6721</v>
@@ -2458,7 +2458,7 @@
         <v>4.871999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1456000000000002</v>
+        <v>0.1456000000000004</v>
       </c>
       <c r="L26" t="n">
         <v>4.726700000000001</v>
@@ -2482,13 +2482,13 @@
         <v>16.6043</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.443300000000001</v>
+        <v>-4.4431</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.3129</v>
+        <v>-6.313099999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8699</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
         <v>1.163900000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484237_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484237_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3991</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,28 +819,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3918</v>
+        <v>1.0848</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8365</v>
+        <v>0.5295</v>
       </c>
       <c r="F5" t="n">
         <v>0.5553</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3358</v>
+        <v>0.0289</v>
       </c>
       <c r="H5" t="n">
-        <v>1.429</v>
+        <v>1.122</v>
       </c>
       <c r="I5" t="n">
         <v>-1.0932</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4951</v>
+        <v>1.1882</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3737</v>
+        <v>1.0668</v>
       </c>
       <c r="L5" t="n">
         <v>0.1214</v>
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-1.6177</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5373</v>
+        <v>0.614</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1786</v>
+        <v>0.614</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7159</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.036</v>
+        <v>0.614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2251</v>
+        <v>0.614</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1891</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1023</v>
+        <v>0.614</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5091</v>
+        <v>0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1383</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7342</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9003</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0997</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4093</v>
+        <v>0.5373</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9774</v>
+        <v>-2.1786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5681</v>
+        <v>2.7159</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1709</v>
+        <v>0.036</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.2251</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6473</v>
+        <v>-0.1891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9762</v>
+        <v>-1.1023</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3287</v>
+        <v>-0.5091</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6475</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1948</v>
+        <v>1.1383</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1949</v>
+        <v>0.7342</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>0.4041</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2132</v>
+        <v>0.9003</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>-0.0997</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4553</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9414</v>
+        <v>-0.3991</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6318</v>
+        <v>0.307</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8793</v>
+        <v>0.307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2475</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0912</v>
+        <v>0.307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4971</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5942</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5949</v>
+        <v>0.307</v>
       </c>
       <c r="K9" t="n">
-        <v>0.921</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6739</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5036</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0797</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1603</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.544</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3837</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1951</v>
+        <v>-0.4093</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8119</v>
+        <v>-0.9774</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6168</v>
+        <v>0.5681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6578000000000001</v>
+        <v>1.1709</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3479</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3099</v>
+        <v>0.6473</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7376</v>
+        <v>0.9762</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.3287</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0.6475</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.1948</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3492</v>
+        <v>0.1949</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2694</v>
+        <v>-0.0002</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4643</v>
+        <v>0.2132</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.2421</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3961</v>
+        <v>0.4553</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3405</v>
+        <v>0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6763</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4316</v>
+        <v>-1.1951</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7134</v>
+        <v>-1.8119</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.145</v>
+        <v>0.6168</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4831</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1264</v>
+        <v>0.3479</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6433</v>
+        <v>0.3099</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5958</v>
+        <v>0.7376</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8898</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2939</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1127</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7634</v>
+        <v>-0.3492</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3494</v>
+        <v>0.2694</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3872</v>
+        <v>0.4643</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4835</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.3961</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9414</v>
+        <v>-1.3405</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>-0.6763</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6106</v>
+        <v>-1.2458</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.918</v>
+        <v>-1.4932</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6926</v>
+        <v>0.2475</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9048</v>
+        <v>0.4773</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1428</v>
+        <v>-0.1169</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0476</v>
+        <v>0.5942</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7335</v>
+        <v>1.9809</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7015</v>
+        <v>0.307</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.968</v>
+        <v>1.6739</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6382</v>
+        <v>-1.5036</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5587</v>
+        <v>-0.4239</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0795</v>
+        <v>-1.0797</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5337</v>
+        <v>-0.1603</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5846</v>
+        <v>-0.544</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0508</v>
+        <v>0.3837</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.278599999999999</v>
+        <v>-1.4316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5490000000000009</v>
+        <v>0.7134</v>
       </c>
       <c r="F13" t="n">
-        <v>7.729599999999999</v>
+        <v>-2.145</v>
       </c>
       <c r="G13" t="n">
-        <v>9.579800000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="H13" t="n">
-        <v>17.6723</v>
+        <v>3.1264</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.091999999999999</v>
+        <v>-2.6433</v>
       </c>
       <c r="J13" t="n">
-        <v>14.4523</v>
+        <v>2.5958</v>
       </c>
       <c r="K13" t="n">
-        <v>17.818</v>
+        <v>3.8898</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3655</v>
+        <v>-1.2939</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.872</v>
+        <v>-2.1127</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1457000000000001</v>
+        <v>-0.7634</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.726599999999999</v>
+        <v>-1.3494</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.883599999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.6039</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7207</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>4.745900000000001</v>
+        <v>-0.3872</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5675</v>
+        <v>-0.4835</v>
       </c>
       <c r="U13" t="n">
-        <v>6.313299999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1639</v>
+        <v>-0.9414</v>
       </c>
       <c r="W13" t="n">
-        <v>4.268</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.4319</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2534</v>
+        <v>-1.6106</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6644</v>
+        <v>-0.918</v>
       </c>
       <c r="F14" t="n">
-        <v>0.589</v>
+        <v>-0.6926</v>
       </c>
       <c r="G14" t="n">
-        <v>3.764</v>
+        <v>-0.9048</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2553</v>
+        <v>2.1428</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0193</v>
+        <v>-3.0476</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7561</v>
+        <v>0.7335</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0056</v>
+        <v>2.7015</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7505</v>
+        <v>-1.968</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9921</v>
+        <v>-1.6382</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2609</v>
+        <v>-0.5587</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2688</v>
+        <v>-1.0795</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7841</v>
+        <v>-0.5337</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0481</v>
+        <v>-0.5846</v>
       </c>
       <c r="U14" t="n">
-        <v>0.264</v>
+        <v>0.0508</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8828</v>
+        <v>0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2224</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3271</v>
+        <v>8.278599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4184</v>
+        <v>0.5491000000000005</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9087</v>
+        <v>7.729599999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9103</v>
+        <v>9.58</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1141</v>
+        <v>17.6723</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0245</v>
+        <v>-8.091999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0929</v>
+        <v>14.4524</v>
       </c>
       <c r="K15" t="n">
-        <v>2.012</v>
+        <v>17.8181</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0809</v>
+        <v>-3.3655</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1826</v>
+        <v>-4.872</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1261</v>
+        <v>-0.1456999999999998</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9435</v>
+        <v>-4.726599999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-16.6039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>11.7207</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8605</v>
+        <v>4.7459</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8067</v>
+        <v>-1.5675</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0537</v>
+        <v>6.313299999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>-1.1639</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3276</v>
+        <v>4.268</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3869</v>
-      </c>
+        <v>-5.4319</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6505</v>
+        <v>5.2534</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6516999999999999</v>
+        <v>4.6644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9988</v>
+        <v>0.589</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9412</v>
+        <v>3.764</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.177</v>
+        <v>-0.2553</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1182</v>
+        <v>4.0193</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2768</v>
+        <v>5.7561</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1023</v>
+        <v>2.0056</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1745</v>
+        <v>3.7505</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6644</v>
+        <v>-1.9921</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2793</v>
+        <v>-2.2609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9437</v>
+        <v>0.2688</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8302</v>
+        <v>-0.7841</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6252</v>
+        <v>-1.0481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.205</v>
+        <v>0.264</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>1.8828</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1704</v>
+        <v>4.3271</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0181</v>
+        <v>3.4184</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1885</v>
+        <v>0.9087</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9889</v>
+        <v>0.9103</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8583</v>
+        <v>-0.1141</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8472</v>
+        <v>1.0245</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0784</v>
+        <v>2.0929</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3095</v>
+        <v>2.012</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7688</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0895</v>
+        <v>-1.1826</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1678</v>
+        <v>-2.1261</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0784</v>
+        <v>0.9435</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0371</v>
+        <v>-0.8605</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1663</v>
+        <v>-0.8067</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1292</v>
+        <v>-0.0537</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3276</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.309</v>
+        <v>1.6505</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2856</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0233</v>
+        <v>0.9988</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6462</v>
+        <v>1.9412</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6324</v>
+        <v>-0.177</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0138</v>
+        <v>2.1182</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5527</v>
+        <v>1.2768</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6741</v>
+        <v>0.1023</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>1.1745</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0935</v>
+        <v>0.6644</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9583</v>
+        <v>-0.2793</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1352</v>
+        <v>0.9437</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2758</v>
+        <v>-0.8302</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5646</v>
+        <v>-0.6252</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2888</v>
+        <v>-0.205</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8317</v>
+        <v>-1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2455</v>
+        <v>0.1704</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3277</v>
+        <v>-2.0181</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9179</v>
+        <v>2.1885</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2124</v>
+        <v>0.9889</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7805</v>
+        <v>-0.8583</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4319</v>
+        <v>1.8472</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0347</v>
+        <v>1.0784</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6127</v>
+        <v>0.3095</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6475</v>
+        <v>0.7688</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2472</v>
+        <v>-0.0895</v>
       </c>
       <c r="N19" t="n">
         <v>-1.1678</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0793</v>
+        <v>1.0784</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0172</v>
+        <v>-0.0371</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3624</v>
+        <v>-0.1663</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3796</v>
+        <v>0.1292</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.802</v>
+        <v>-0.309</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2622</v>
+        <v>-0.2856</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5397</v>
+        <v>-0.0233</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4519</v>
+        <v>-1.6462</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4884</v>
+        <v>-1.6324</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0365</v>
+        <v>-0.0138</v>
       </c>
       <c r="J20" t="n">
-        <v>0.656</v>
+        <v>-0.5527</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5718</v>
+        <v>-0.6741</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2278</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1079</v>
+        <v>-1.0935</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9166</v>
+        <v>-0.9583</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8087</v>
+        <v>-0.1352</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5454</v>
+        <v>-0.2758</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7462</v>
+        <v>-0.5646</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2008</v>
+        <v>0.2888</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>0.8317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3062</v>
+        <v>-1.2455</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2675</v>
+        <v>-0.3277</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0387</v>
+        <v>-0.9179</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5085</v>
+        <v>-2.2124</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8383</v>
+        <v>-1.7805</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6701</v>
+        <v>-0.4319</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3913</v>
+        <v>0.0347</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1433</v>
+        <v>-0.6127</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5345</v>
+        <v>0.6475</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1172</v>
+        <v>-2.2472</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9816</v>
+        <v>-1.1678</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1356</v>
+        <v>-1.0793</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3954</v>
+        <v>-0.3624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3205</v>
+        <v>0.3796</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4959</v>
+        <v>-0.2224</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8791</v>
+        <v>-1.802</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1521</v>
+        <v>-1.2622</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7269</v>
+        <v>-0.5397</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0584</v>
+        <v>-0.4519</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5943</v>
+        <v>-2.4884</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5359</v>
+        <v>2.0365</v>
       </c>
       <c r="J22" t="n">
-        <v>1.659</v>
+        <v>0.656</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.5718</v>
       </c>
       <c r="L22" t="n">
-        <v>2.5365</v>
+        <v>1.2278</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7174</v>
+        <v>-1.1079</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7168</v>
+        <v>-1.9166</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.8087</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6486</v>
+        <v>-0.5454</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6857</v>
+        <v>-0.7462</v>
       </c>
       <c r="U22" t="n">
-        <v>0.037</v>
+        <v>0.2008</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6093</v>
@@ -2186,12 +2287,17 @@
       </c>
       <c r="X22" t="n">
         <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0436</v>
+        <v>-2.3062</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.138</v>
+        <v>-2.2675</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9056</v>
+        <v>-0.0387</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.37</v>
+        <v>-4.5085</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6122</v>
+        <v>-1.8383</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2422</v>
+        <v>-2.6701</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.448</v>
+        <v>-2.3913</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0167</v>
+        <v>0.1433</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4313</v>
+        <v>-2.5345</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9221</v>
+        <v>-2.1172</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.5956</v>
+        <v>-1.9816</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6735</v>
+        <v>-0.1356</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2325</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1663</v>
+        <v>-0.3954</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3988</v>
+        <v>0.3205</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8828</v>
+        <v>1.4959</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.3283</v>
+        <v>1.4959</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6928</v>
+        <v>-2.8791</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5473</v>
+        <v>-2.1521</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1455</v>
+        <v>-0.7269</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.287</v>
+        <v>-0.0584</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7094</v>
+        <v>-2.5943</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5776</v>
+        <v>2.5359</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.3285</v>
+        <v>1.659</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0207</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3077</v>
+        <v>2.5365</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9585</v>
+        <v>-1.7174</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6887</v>
+        <v>-1.7168</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2698</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2105</v>
+        <v>-0.6486</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2421</v>
+        <v>-0.6857</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0316</v>
+        <v>0.037</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0993</v>
+        <v>-3.0436</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4655</v>
+        <v>-2.138</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6338</v>
+        <v>-0.9056</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6502</v>
+        <v>-2.37</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6119</v>
+        <v>-2.6122</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0383</v>
+        <v>0.2422</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9614</v>
+        <v>-0.448</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6536</v>
+        <v>-0.0167</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3077</v>
+        <v>-0.4313</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6889</v>
+        <v>-1.9221</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9583</v>
+        <v>-2.5956</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2694</v>
+        <v>0.6735</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4257</v>
+        <v>0.2325</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5041</v>
+        <v>-0.1663</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0784</v>
+        <v>0.3988</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2186</v>
+        <v>-1.8828</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-3.6928</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.5473</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.1455</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.287</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.7094</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.5776</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.3285</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.0207</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.9585</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6887</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2105</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2421</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F. DIAZ CABANAS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.0993</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.4655</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.6338</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.6502</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.6119</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.0383</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.9614</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.6536</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.6889</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.9583</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4257</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.5041</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484237_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-7.976100000000001</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>-7.729500000000002</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>-0.2463999999999995</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>-9.580199999999998</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H28" t="n">
         <v>-17.6721</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>8.0921</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>4.871999999999999</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>0.1456000000000004</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>4.726700000000001</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>-14.4525</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>-17.8178</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>3.3655</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>4.883699999999999</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-11.7205</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>16.6043</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>-4.4431</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>-6.313099999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>1.87</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>1.163900000000001</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>5.4321</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-4.2682</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
